--- a/ESG_GHG_Benchmark_Poland_2025.xlsx
+++ b/ESG_GHG_Benchmark_Poland_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matteodegianni/Desktop/Jobs/Materiality Data Analyst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA82A85-447D-9649-8E44-89C1F0369D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7F12EA6-5DD0-D342-9633-AF09AFC2830F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="660" windowWidth="29400" windowHeight="17380" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="29400" windowHeight="17380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="225">
   <si>
     <t>Polish Corporate GHG Benchmark (ESRS E1, reporting year 2025)</t>
   </si>
@@ -485,15 +485,6 @@
     <t>Methodology unclear</t>
   </si>
   <si>
-    <t>Scope 2 market-based (207,858 t) higher than location-based (135,019 t): no guarantees of origin, residual mix factor 808.3 vs grid average 524.9 tCO2/GWh</t>
-  </si>
-  <si>
-    <t>MB total higher than LB; not an error</t>
-  </si>
-  <si>
-    <t>Kept both values; totals use MB</t>
-  </si>
-  <si>
     <t>Scope 3 is 96.6% of total; category 1 (purchased goods) is spend-based using Climatiq factors. Company states high measurement uncertainty</t>
   </si>
   <si>
@@ -524,18 +515,6 @@
     <t>Recorded as 0%, flagged</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>No GHG reduction targets disclosed (E1-6 target columns empty, no formal transition plan in E1-1)</t>
-  </si>
-  <si>
-    <t>Cannot assess progress against targets</t>
-  </si>
-  <si>
-    <t>Noted in README</t>
-  </si>
-  <si>
     <t>Emissions include Mall South (Slovenia, Croatia; held for sale at 31.12.2025, SPA signed 7 Jan 2026). Its revenue (PLN 427.7m) sits in discontinued operations (note 18.2) and was added back to match the emissions boundary</t>
   </si>
   <si>
@@ -545,9 +524,6 @@
     <t>Revenue = 11,458.1 + 427.7 = 11,885.8 PLN m</t>
   </si>
   <si>
-    <t>Reported intensity (35.1) uses revenue plus other operating income incl. discontinued (PLN 12,103.4m). Net revenue only gives 35.8 (+2.0%)</t>
-  </si>
-  <si>
     <t>Reported intensity slightly understated vs strict net revenue</t>
   </si>
   <si>
@@ -608,12 +584,6 @@
     <t>Small boundary differences across companies</t>
   </si>
   <si>
-    <t>Scope 2 market-based 97% below location-based (7,354 vs 272,838 t): 100% renewable electricity via PPAs and guarantees of origin without PPA (114,028 MWh)</t>
-  </si>
-  <si>
-    <t>Market-based progress relies on contractual instruments</t>
-  </si>
-  <si>
     <t>Kept both values</t>
   </si>
   <si>
@@ -626,21 +596,9 @@
     <t>Franchise model: emissions of franchised stores (242,231 t) are in Scope 3 category 14, while Dino reports store energy in Scope 1 and 2</t>
   </si>
   <si>
-    <t>Scope 1+2 and per-employee KPIs not comparable between Dino and Zabka; use total intensity</t>
-  </si>
-  <si>
     <t>Compare food retailers on total (S1+2+3) intensity only</t>
   </si>
   <si>
-    <t>Only 4,257 employees (headcount): franchisee staff are not Group employees (Dino: 55,856)</t>
-  </si>
-  <si>
-    <t>Emissions per employee meaningless across business models</t>
-  </si>
-  <si>
-    <t>Excluded from cross-company comparison</t>
-  </si>
-  <si>
     <t>Location-based total (3,592,616 t) exceeds Scope 1 + Scope 2 LB + reported Scope 3 by 155,536 t; likely Scope 3 (e.g. franchise electricity) recalculated location-based, not disclosed separately</t>
   </si>
   <si>
@@ -692,12 +650,6 @@
     <t>Year-on-year trend slightly distorted</t>
   </si>
   <si>
-    <t>Highest Taxonomy alignment in sample: turnover 25.5% (aluminium window and shading systems, CCM 3.5), CapEx 8.6%, OpEx 38.0%. Previous target (-25% intensity) met in 2024; new absolute Scope 1+2 target with 2024 base year, net zero by 2050</t>
-  </si>
-  <si>
-    <t>Only company with material aligned turnover</t>
-  </si>
-  <si>
     <t>Report gives parent company (Table 125) and Group (Table 126) separately; Group used. Joint ventures are reported in Scope 3 category 15 (1,099,433 t, 43.5% of Scope 3)</t>
   </si>
   <si>
@@ -707,27 +659,12 @@
     <t>Group figures used; cat. 15 flagged</t>
   </si>
   <si>
-    <t>77.9% of Scope 1 covered by EU ETS: only company in sample with regulated emissions so far</t>
-  </si>
-  <si>
-    <t>Carbon cost exposure, not comparable with retail</t>
-  </si>
-  <si>
-    <t>Scope 2 market-based (2,105,896 t) 35% above location-based (1,554,657 t) and up 9.4% YoY; parent company S1+2 MB is +10.5% vs 2020 base year against a -30% by 2030 target</t>
-  </si>
-  <si>
-    <t>Moving away from target on market-based view</t>
-  </si>
-  <si>
     <t>Scope 3 category 1 fell 46.5% and category 4 fell 45.3% YoY without explanation in the report; Scope 3 total -21.5%</t>
   </si>
   <si>
     <t>Year-on-year Scope 3 trend unreliable</t>
   </si>
   <si>
-    <t>Taxonomy alignment not assessed in 2025 (footnote 57), although 2024 reported aligned turnover 0.87%, CapEx 3.92%, OpEx 2.04%. Table captions say 2024 but data are 2025</t>
-  </si>
-  <si>
     <t>0% means not assessed; drop vs 2024 is a reporting change</t>
   </si>
   <si>
@@ -755,27 +692,9 @@
     <t>Group total from main E1-6 table used</t>
   </si>
   <si>
-    <t>Scope 1 is 67% of total and 98.98% under EU ETS; Scope 3 dominated by category 3 (21.3 Mt, 89%), calculated only with database factors, no supplier data. Energy consumption (149.5 TWh) includes fuel burned for power generation</t>
-  </si>
-  <si>
-    <t>Energy and emission intensities not comparable with non-utilities</t>
-  </si>
-  <si>
     <t>Compare utilities only with each other</t>
   </si>
   <si>
-    <t>High Taxonomy alignment: turnover 24.6% (grids CCM 4.9, wind CCM 4.3, rail infrastructure), CapEx 42.9%, OpEx 41.2%, while total emissions remain the highest in the sample</t>
-  </si>
-  <si>
-    <t>Green investment coexists with coal-heavy generation</t>
-  </si>
-  <si>
-    <t>Scope 1 rose 6.3% YoY (9.24 to 9.83 Mt) due to higher coal-fired generation; 98% under EU ETS. Scope 1 is 71% of the 2022 base year; targets shown as 29% of base by 2030 and 0% by 2040</t>
-  </si>
-  <si>
-    <t>Utility emissions driven by dispatch, not structural trend</t>
-  </si>
-  <si>
     <t>Scope 2 includes purchased electricity covering distribution grid losses (loss rate 3.5% in 2025 vs 2% in 2024), so Scope 2 LB rose 57% YoY</t>
   </si>
   <si>
@@ -794,12 +713,6 @@
     <t>Energy YoY change partly boundary-driven</t>
   </si>
   <si>
-    <t>Highest Taxonomy alignment in sample: turnover 38.8%, CapEx 84.5%, OpEx 74.2% (grids and renewables), despite 26.8 Mt total emissions. Intensity disclosed with 6 decimals (0.000807 t/PLN): precise, computed 806.8 matches</t>
-  </si>
-  <si>
-    <t>Green investment coexists with coal generation (as for PGE)</t>
-  </si>
-  <si>
     <t>Total_MB_t</t>
   </si>
   <si>
@@ -810,6 +723,15 @@
   </si>
   <si>
     <t>Check_vs_Formula</t>
+  </si>
+  <si>
+    <t>Reported intensity (35.1) is reproduced only with revenue plus other operating income incl. discontinued (PLN 12,103.4m). Net revenue only gives 35.8 (+2.0%)</t>
+  </si>
+  <si>
+    <t>Scope 1+2 not comparable with Dino; only total (Scope 1+2+3) intensity is comparable</t>
+  </si>
+  <si>
+    <t>Taxonomy alignment not assessed in 2025 (footnote 57), although 2024 reported aligned turnover 0.87%, CapEx 3.92%, OpEx 2.04%</t>
   </si>
 </sst>
 </file>
@@ -932,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -964,9 +886,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1948,19 +1876,19 @@
         <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="E1" t="s">
         <v>116</v>
       </c>
       <c r="F1" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>250</v>
+        <v>220</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18">
@@ -1985,7 +1913,7 @@
       <c r="G2">
         <v>2433.4048084122796</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="22">
         <f>ROUND(F2-_xlfn.XLOOKUP(A2,Calculations!A:A,Calculations!L:L),6)</f>
         <v>0</v>
       </c>
@@ -4067,7 +3995,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
@@ -4493,699 +4421,589 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:5" ht="42">
+      <c r="A19" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="25" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:5" ht="28">
+      <c r="A20" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="25" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:5" ht="42">
+      <c r="A21" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="56">
+      <c r="A22" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="42">
+      <c r="A23" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C23" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28">
+      <c r="A24" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="42">
+      <c r="A25" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="C25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="84">
+      <c r="A26" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28">
+      <c r="A27" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="42">
+      <c r="A28" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="42">
+      <c r="A29" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28">
+      <c r="A30" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="11" t="s">
+    </row>
+    <row r="31" spans="1:5" ht="42">
+      <c r="A31" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="56">
+      <c r="A32" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="42">
+      <c r="A33" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="42">
+      <c r="A34" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="11" t="s">
+    </row>
+    <row r="35" spans="1:5" ht="42">
+      <c r="A35" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="42">
+      <c r="A36" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="42">
+      <c r="A37" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28">
+      <c r="A38" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E38" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1">
-      <c r="A25" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="11" t="s">
+    </row>
+    <row r="39" spans="1:5" ht="56">
+      <c r="A39" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="42">
+      <c r="A40" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="C40" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="42">
+      <c r="A41" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="42">
+      <c r="A42" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1">
-      <c r="A27" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="C42" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="42">
+      <c r="A43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1">
-      <c r="A31" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="C43" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="56">
+      <c r="A44" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="11" t="s">
+      <c r="C44" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="42">
+      <c r="A45" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1">
-      <c r="A37" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1">
-      <c r="A38" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1">
-      <c r="A39" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1">
-      <c r="A40" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="21" t="s">
+      <c r="C45" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="42">
+      <c r="A46" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1">
-      <c r="A41" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1">
-      <c r="A42" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1">
-      <c r="A43" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1">
-      <c r="A44" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D44" s="21" t="s">
+      <c r="C46" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="D46" s="25" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="15" customHeight="1">
-      <c r="A45" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="21" t="s">
+      <c r="E46" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="28">
+      <c r="A47" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D47" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="E45" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1">
-      <c r="A46" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1">
-      <c r="A47" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>168</v>
+      <c r="E47" s="25" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
-      <c r="A48" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>154</v>
-      </c>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
-      <c r="A49" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>226</v>
-      </c>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
-      <c r="A50" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>147</v>
-      </c>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
-      <c r="A51" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>231</v>
-      </c>
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1">
-      <c r="A52" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>234</v>
-      </c>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1">
-      <c r="A53" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>158</v>
-      </c>
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
-      <c r="A54" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>158</v>
-      </c>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1">
-      <c r="A55" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>234</v>
-      </c>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1">
-      <c r="A56" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>168</v>
-      </c>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1">
-      <c r="A57" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>168</v>
-      </c>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1">
-      <c r="A58" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>158</v>
-      </c>
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
     </row>
   </sheetData>
   <dataValidations count="1">
